--- a/data/trans_dic/P33B_R1-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R1-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,46; 13,71</t>
+          <t>8,27; 13,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,22; 16,14</t>
+          <t>11,2; 16,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,38; 14,25</t>
+          <t>10,28; 14,19</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,42; 14,47</t>
+          <t>8,45; 14,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,09; 20,92</t>
+          <t>14,63; 21,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,11; 16,48</t>
+          <t>12,18; 16,55</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 18,8</t>
+          <t>13,3; 20,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,33; 33,1</t>
+          <t>21,13; 33,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,2; 20,92</t>
+          <t>16,52; 22,4</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,11; 15,02</t>
+          <t>11,16; 15,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,28; 18,92</t>
+          <t>16,21; 20,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,95; 15,64</t>
+          <t>14,09; 16,92</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,59; 17,85</t>
+          <t>10,66; 16,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,67; 27,45</t>
+          <t>24,37; 29,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,25; 22,71</t>
+          <t>19,51; 23,23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,98; 16,56</t>
+          <t>5,35; 17,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,69; 27,02</t>
+          <t>21,44; 27,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,2; 23,32</t>
+          <t>18,71; 23,59</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,55; 13,5</t>
+          <t>11,6; 13,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,98; 21,21</t>
+          <t>20,37; 22,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,57; 17,16</t>
+          <t>16,35; 18,03</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55452</t>
+          <t>59057</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60401</t>
+          <t>66754</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>115853</t>
+          <t>125811</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>42748; 69285</t>
+          <t>45560; 75692</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50205; 72203</t>
+          <t>54720; 80565</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98909; 135783</t>
+          <t>106830; 147469</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>50752</t>
+          <t>53420</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>66728</t>
+          <t>74939</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>117480</t>
+          <t>128359</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38092; 65415</t>
+          <t>40829; 68824</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53888; 80049</t>
+          <t>61894; 89630</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>101074; 137567</t>
+          <t>110356; 150042</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74602</t>
+          <t>78888</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44511</t>
+          <t>49966</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>119113</t>
+          <t>128854</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28790; 125606</t>
+          <t>62708; 94774</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35486; 55062</t>
+          <t>39495; 62419</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51710; 174637</t>
+          <t>108816; 147524</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>134738</t>
+          <t>147930</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>140719</t>
+          <t>160302</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275456</t>
+          <t>308232</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>114973; 155419</t>
+          <t>126348; 170696</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80967; 185081</t>
+          <t>139568; 178799</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>180255; 314818</t>
+          <t>280907; 337135</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>68044</t>
+          <t>75721</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>199052</t>
+          <t>222868</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>267095</t>
+          <t>298589</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>54959; 84627</t>
+          <t>60442; 92370</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>148290; 230279</t>
+          <t>202306; 244183</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>213426; 298206</t>
+          <t>272565; 324589</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>22920</t>
+          <t>22614</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>183867</t>
+          <t>204617</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>206787</t>
+          <t>227231</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11970; 39825</t>
+          <t>12699; 41028</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>165154; 205700</t>
+          <t>181026; 229407</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>182335; 233667</t>
+          <t>202326; 255118</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>406507</t>
+          <t>437630</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>695278</t>
+          <t>779446</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1101785</t>
+          <t>1217075</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>322255; 455755</t>
+          <t>399040; 477770</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>571235; 758369</t>
+          <t>740318; 822938</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>942756; 1192321</t>
+          <t>1157090; 1275861</t>
         </is>
       </c>
     </row>
